--- a/WpfClient/Resources/ConsumablesTemplate.xlsx
+++ b/WpfClient/Resources/ConsumablesTemplate.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thron\source\repos\RequestManagementSystem\WpfClient\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Thron\source\repos\Thron41k\RequestManagementSystem\WpfClient\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{600CACAA-E2F2-49DA-8EF9-828340FAE33B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26DCCA1B-F576-469A-89D0-66A0BDE1EB1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="26">
   <si>
     <t>Приложение № 15</t>
   </si>
@@ -98,6 +98,12 @@
   </si>
   <si>
     <t>Материально - ответственное лицо:</t>
+  </si>
+  <si>
+    <t>Объект (номенклатурная группа):</t>
+  </si>
+  <si>
+    <t>СОДЕРЖАНИЕ АВТОМОБИЛЬНОЙ ДОРОГИ АМУР И ИССО КМ 380+000 - КМ 741 + 775</t>
   </si>
 </sst>
 </file>
@@ -176,7 +182,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="20">
     <border>
       <left/>
       <right/>
@@ -386,11 +392,20 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -428,98 +443,101 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -829,7 +847,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J34"/>
+  <dimension ref="A1:J36"/>
   <sheetFormatPr defaultColWidth="10.5" defaultRowHeight="11.45" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="23.6640625" style="1" customWidth="1"/>
@@ -856,45 +874,45 @@
     </row>
     <row r="3" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="13"/>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
       <c r="H4" s="3" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="15"/>
-      <c r="H5" s="38"/>
-      <c r="I5" s="38"/>
-      <c r="J5" s="38"/>
+      <c r="B5" s="43"/>
+      <c r="C5" s="43"/>
+      <c r="D5" s="43"/>
+      <c r="H5" s="40"/>
+      <c r="I5" s="40"/>
+      <c r="J5" s="40"/>
     </row>
     <row r="6" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="H6" s="14" t="s">
+      <c r="H6" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
     </row>
     <row r="7" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G7" s="39"/>
-      <c r="H7" s="39"/>
-      <c r="I7" s="39"/>
-      <c r="J7" s="39"/>
+      <c r="G7" s="42"/>
+      <c r="H7" s="42"/>
+      <c r="I7" s="42"/>
+      <c r="J7" s="42"/>
     </row>
     <row r="8" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="G8" s="16" t="s">
+      <c r="G8" s="35" t="s">
         <v>5</v>
       </c>
-      <c r="H8" s="16"/>
-      <c r="I8" s="16"/>
-      <c r="J8" s="16"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
     </row>
     <row r="9" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="10" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
@@ -903,17 +921,17 @@
     <row r="11" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="12" spans="1:10" ht="23.1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D12" s="7"/>
-      <c r="E12" s="17" t="s">
+      <c r="E12" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="17"/>
+      <c r="F12" s="36"/>
       <c r="G12" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="17"/>
+      <c r="I12" s="36"/>
       <c r="J12" s="8" t="s">
         <v>9</v>
       </c>
@@ -922,254 +940,271 @@
       <c r="D13" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="18"/>
-      <c r="F13" s="18"/>
-      <c r="G13" s="43"/>
-      <c r="H13" s="19"/>
-      <c r="I13" s="19"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="38"/>
+      <c r="I13" s="38"/>
       <c r="J13" s="11"/>
     </row>
     <row r="14" spans="1:10" ht="15.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="20" t="s">
+      <c r="A14" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="20"/>
-      <c r="I14" s="20"/>
-      <c r="J14" s="20"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="31"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="31"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="31"/>
     </row>
     <row r="15" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="16" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C16" s="44" t="s">
+        <v>25</v>
+      </c>
+      <c r="D16" s="44"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="44"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+    </row>
+    <row r="17" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="18" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="C16" s="36"/>
-      <c r="D16" s="36"/>
-      <c r="F16" s="37"/>
-      <c r="G16" s="37"/>
-      <c r="H16" s="37"/>
-      <c r="I16" s="37"/>
-      <c r="J16" s="37"/>
-    </row>
-    <row r="17" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="21" t="s">
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="33"/>
+      <c r="J18" s="33"/>
+    </row>
+    <row r="19" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="D17" s="21"/>
-      <c r="F17" s="21" t="s">
+      <c r="D19" s="34"/>
+      <c r="F19" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
-      <c r="J17" s="21"/>
-    </row>
-    <row r="18" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="22" t="s">
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+    </row>
+    <row r="20" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="23" t="s">
         <v>15</v>
       </c>
-      <c r="B18" s="22"/>
-      <c r="C18" s="22" t="s">
+      <c r="B20" s="23"/>
+      <c r="C20" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="D18" s="26" t="s">
+      <c r="D20" s="27" t="s">
         <v>17</v>
       </c>
-      <c r="E18" s="26"/>
-      <c r="F18" s="22" t="s">
+      <c r="E20" s="27"/>
+      <c r="F20" s="23" t="s">
         <v>18</v>
       </c>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-    </row>
-    <row r="19" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="23"/>
-      <c r="B19" s="24"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="27"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="23"/>
-      <c r="G19" s="29"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="29"/>
-      <c r="J19" s="24"/>
-    </row>
-    <row r="20" spans="1:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="30"/>
-      <c r="B20" s="30"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="31"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-    </row>
-    <row r="21" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="30"/>
-      <c r="B21" s="30"/>
-      <c r="C21" s="12"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="31"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="32"/>
-      <c r="I21" s="32"/>
-      <c r="J21" s="32"/>
-    </row>
-    <row r="22" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
+      <c r="G20" s="23"/>
+      <c r="H20" s="23"/>
+      <c r="I20" s="23"/>
+      <c r="J20" s="23"/>
+    </row>
+    <row r="21" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="26"/>
+      <c r="D21" s="28"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="30"/>
+      <c r="I21" s="30"/>
+      <c r="J21" s="25"/>
+    </row>
+    <row r="22" spans="1:10" ht="13.35" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="20"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="12"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
+      <c r="J22" s="22"/>
+    </row>
+    <row r="23" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="20"/>
+      <c r="B23" s="20"/>
+      <c r="C23" s="12"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
+      <c r="J23" s="22"/>
+    </row>
+    <row r="24" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="3" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B23" s="40"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-      <c r="F23" s="5"/>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41"/>
-    </row>
-    <row r="24" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B24" s="4" t="s">
+    <row r="25" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="13"/>
+      <c r="D25" s="5"/>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
+    </row>
+    <row r="26" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B26" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D24" s="33" t="s">
+      <c r="D26" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E24" s="33"/>
-      <c r="F24" s="33"/>
-      <c r="H24" s="33" t="s">
+      <c r="E26" s="19"/>
+      <c r="F26" s="19"/>
+      <c r="H26" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="I24" s="33"/>
-    </row>
-    <row r="25" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
+      <c r="I26" s="19"/>
+    </row>
+    <row r="27" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="3" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B26" s="40"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-      <c r="F26" s="5"/>
-      <c r="H26" s="41"/>
-      <c r="I26" s="41"/>
-    </row>
-    <row r="27" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B27" s="4" t="s">
+    <row r="28" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B28" s="13"/>
+      <c r="D28" s="5"/>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
+    </row>
+    <row r="29" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B29" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D27" s="33" t="s">
+      <c r="D29" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E27" s="33"/>
-      <c r="F27" s="33"/>
-      <c r="H27" s="33" t="s">
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="H29" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="I27" s="33"/>
-    </row>
-    <row r="28" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B29" s="40"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-      <c r="F29" s="5"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-    </row>
-    <row r="30" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B30" s="4" t="s">
+      <c r="I29" s="19"/>
+    </row>
+    <row r="30" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="31" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B31" s="13"/>
+      <c r="D31" s="5"/>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
+    </row>
+    <row r="32" spans="1:10" ht="11.1" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B32" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D30" s="33" t="s">
+      <c r="D32" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="33"/>
-      <c r="F30" s="33"/>
-      <c r="H30" s="33" t="s">
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="H32" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="33"/>
-    </row>
-    <row r="31" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:10" ht="12.95" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" spans="1:9" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="34" t="s">
+      <c r="I32" s="19"/>
+    </row>
+    <row r="33" spans="1:9" ht="12.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="34" spans="1:9" ht="12.95" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="35" spans="1:9" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="B33" s="42"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-      <c r="F33" s="5"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
-    </row>
-    <row r="34" spans="1:9" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="35"/>
-      <c r="B34" s="4" t="s">
+      <c r="B35" s="14"/>
+      <c r="D35" s="5"/>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="H35" s="18"/>
+      <c r="I35" s="18"/>
+    </row>
+    <row r="36" spans="1:9" ht="12.95" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="17"/>
+      <c r="B36" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D34" s="33" t="s">
+      <c r="D36" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E34" s="33"/>
-      <c r="F34" s="33"/>
-      <c r="H34" s="33" t="s">
+      <c r="E36" s="19"/>
+      <c r="F36" s="19"/>
+      <c r="H36" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="I34" s="33"/>
+      <c r="I36" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="38">
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="H33:I33"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H29:I29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="H24:I24"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="D21:E21"/>
-    <mergeCell ref="F21:J21"/>
-    <mergeCell ref="A18:B19"/>
-    <mergeCell ref="C18:C19"/>
-    <mergeCell ref="D18:E19"/>
-    <mergeCell ref="F18:J19"/>
-    <mergeCell ref="A20:B20"/>
-    <mergeCell ref="D20:E20"/>
-    <mergeCell ref="F20:J20"/>
-    <mergeCell ref="A14:J14"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="F16:J16"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="F17:J17"/>
+  <mergeCells count="39">
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="H6:J6"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="A5:D5"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="H12:I12"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="H13:I13"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="H6:J6"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A14:J14"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="F18:J18"/>
+    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="F19:J19"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="D20:E21"/>
+    <mergeCell ref="F20:J21"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="D22:E22"/>
+    <mergeCell ref="F22:J22"/>
+    <mergeCell ref="H25:I25"/>
+    <mergeCell ref="D26:F26"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="D23:E23"/>
+    <mergeCell ref="F23:J23"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="D36:F36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="H28:I28"/>
+    <mergeCell ref="D29:F29"/>
+    <mergeCell ref="H29:I29"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="D32:F32"/>
+    <mergeCell ref="H32:I32"/>
   </mergeCells>
   <pageMargins left="0.39370078740157483" right="0.39370078740157483" top="0.39370078740157483" bottom="0.39370078740157483" header="0" footer="0"/>
   <pageSetup paperSize="9" fitToHeight="0" pageOrder="overThenDown" orientation="portrait"/>
